--- a/exports/trend_1d/CROMPTON_full_report.xlsx
+++ b/exports/trend_1d/CROMPTON_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:U55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>13.54</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42628</v>
+        <v>42629</v>
       </c>
       <c r="H2" t="n">
-        <v>160.45</v>
+        <v>155.8</v>
       </c>
       <c r="I2" t="n">
         <v>158.8725380076966</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K2" t="n">
-        <v>21.37</v>
+        <v>17.85</v>
       </c>
       <c r="L2" t="n">
         <v>4.31</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>14.61</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42647</v>
+        <v>42648</v>
       </c>
       <c r="H3" t="n">
-        <v>163.9</v>
+        <v>170.35</v>
       </c>
       <c r="I3" t="n">
         <v>167.2730634698582</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.2</v>
+        <v>-9.34</v>
       </c>
       <c r="L3" t="n">
-        <v>7.61</v>
+        <v>12.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.37</v>
       </c>
       <c r="N3" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="O3" t="n">
         <v>-2.9</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>13.38</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42682</v>
+        <v>42683</v>
       </c>
       <c r="H4" t="n">
-        <v>168.65</v>
+        <v>165.55</v>
       </c>
       <c r="I4" t="n">
         <v>168.3062961583794</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>-1</v>
+        <v>-2.82</v>
       </c>
       <c r="L4" t="n">
-        <v>3.67</v>
+        <v>20.6</v>
       </c>
       <c r="M4" t="n">
-        <v>2.52</v>
+        <v>19.8</v>
       </c>
       <c r="N4" t="n">
         <v>3.93</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42748</v>
+        <v>42751</v>
       </c>
       <c r="H5" t="n">
-        <v>157.3</v>
+        <v>160.3</v>
       </c>
       <c r="I5" t="n">
         <v>158.7230352865091</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K5" t="n">
-        <v>4.98</v>
+        <v>3.17</v>
       </c>
       <c r="L5" t="n">
         <v>3.2</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.25</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H6" t="n">
-        <v>224.9</v>
+        <v>217.3</v>
       </c>
       <c r="I6" t="n">
         <v>217.4176276217342</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K6" t="n">
-        <v>40.3</v>
+        <v>35.56</v>
       </c>
       <c r="L6" t="n">
         <v>1.72</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>14.36</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43045</v>
+        <v>43046</v>
       </c>
       <c r="H7" t="n">
-        <v>223.55</v>
+        <v>229.1</v>
       </c>
       <c r="I7" t="n">
         <v>226.0179207450355</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.88</v>
+        <v>-5.43</v>
       </c>
       <c r="L7" t="n">
         <v>13.16</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.27</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43123</v>
+        <v>43124</v>
       </c>
       <c r="H8" t="n">
-        <v>264.3</v>
+        <v>250.75</v>
       </c>
       <c r="I8" t="n">
         <v>253.3735811957307</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K8" t="n">
-        <v>15.36</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>3.54</v>
@@ -897,7 +992,7 @@
         <v>1.29</v>
       </c>
       <c r="N8" t="n">
-        <v>3.12</v>
+        <v>5.13</v>
       </c>
       <c r="O8" t="n">
         <v>2.48</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>16.98</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43224</v>
+        <v>43227</v>
       </c>
       <c r="H9" t="n">
-        <v>245.1</v>
+        <v>248.9</v>
       </c>
       <c r="I9" t="n">
         <v>246.9361807624528</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K9" t="n">
-        <v>2.25</v>
+        <v>0.74</v>
       </c>
       <c r="L9" t="n">
         <v>7.28</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.65</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43249</v>
+        <v>43250</v>
       </c>
       <c r="H10" t="n">
-        <v>226.4</v>
+        <v>222.05</v>
       </c>
       <c r="I10" t="n">
         <v>224.0585050526611</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.039999999999999</v>
+        <v>-10.79</v>
       </c>
       <c r="L10" t="n">
         <v>11.89</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>14.37</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43301</v>
+        <v>43304</v>
       </c>
       <c r="H11" t="n">
-        <v>235.25</v>
+        <v>240.55</v>
       </c>
       <c r="I11" t="n">
         <v>237.7683577615441</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.94</v>
+        <v>-8.33</v>
       </c>
       <c r="L11" t="n">
-        <v>7.63</v>
+        <v>9.75</v>
       </c>
       <c r="M11" t="n">
         <v>1.45</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43346</v>
+        <v>43347</v>
       </c>
       <c r="H12" t="n">
-        <v>250.4</v>
+        <v>233.8</v>
       </c>
       <c r="I12" t="n">
         <v>243.2767659881557</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K12" t="n">
-        <v>4.09</v>
+        <v>-2.81</v>
       </c>
       <c r="L12" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="M12" t="n">
         <v>0.8</v>
       </c>
       <c r="N12" t="n">
-        <v>5.94</v>
+        <v>6.63</v>
       </c>
       <c r="O12" t="n">
         <v>2.25</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>15.67</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43439</v>
+        <v>43440</v>
       </c>
       <c r="H13" t="n">
-        <v>220.05</v>
+        <v>221.35</v>
       </c>
       <c r="I13" t="n">
         <v>221.0615687505036</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K13" t="n">
-        <v>5.88</v>
+        <v>5.33</v>
       </c>
       <c r="L13" t="n">
         <v>7.74</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.65</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43497</v>
+        <v>43500</v>
       </c>
       <c r="H14" t="n">
-        <v>213.9</v>
+        <v>212.3</v>
       </c>
       <c r="I14" t="n">
         <v>212.5012299810064</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.37</v>
+        <v>-4.09</v>
       </c>
       <c r="L14" t="n">
         <v>6.35</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>12.73</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43531</v>
+        <v>43532</v>
       </c>
       <c r="H15" t="n">
-        <v>218.8</v>
+        <v>220.55</v>
       </c>
       <c r="I15" t="n">
         <v>220.5034937784176</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.06</v>
+        <v>-3.89</v>
       </c>
       <c r="L15" t="n">
         <v>4.78</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>11.6</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43600</v>
+        <v>43601</v>
       </c>
       <c r="H16" t="n">
-        <v>214.2</v>
+        <v>212.05</v>
       </c>
       <c r="I16" t="n">
         <v>212.9042081741979</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.88</v>
+        <v>-3.85</v>
       </c>
       <c r="L16" t="n">
-        <v>3.76</v>
+        <v>4.56</v>
       </c>
       <c r="M16" t="n">
         <v>1.62</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>12.05</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43615</v>
+        <v>43616</v>
       </c>
       <c r="H17" t="n">
-        <v>236.6</v>
+        <v>237.7</v>
       </c>
       <c r="I17" t="n">
         <v>237.2577284651949</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>-11.58</v>
+        <v>-12.1</v>
       </c>
       <c r="L17" t="n">
         <v>13.58</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>10.6</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43698</v>
+        <v>43699</v>
       </c>
       <c r="H18" t="n">
-        <v>225.95</v>
+        <v>223.55</v>
       </c>
       <c r="I18" t="n">
         <v>223.8165261637743</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.94</v>
+        <v>-5.95</v>
       </c>
       <c r="L18" t="n">
-        <v>6.18</v>
+        <v>7.32</v>
       </c>
       <c r="M18" t="n">
         <v>2.4</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>7.97</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H19" t="n">
-        <v>237</v>
+        <v>251.55</v>
       </c>
       <c r="I19" t="n">
         <v>241.3698921651928</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.02</v>
+        <v>-12.53</v>
       </c>
       <c r="L19" t="n">
-        <v>9.6</v>
+        <v>19.15</v>
       </c>
       <c r="M19" t="n">
         <v>0.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>6.14</v>
       </c>
       <c r="O19" t="n">
         <v>-1.06</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>10.4</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43795</v>
+        <v>43796</v>
       </c>
       <c r="H20" t="n">
-        <v>250.1</v>
+        <v>244.15</v>
       </c>
       <c r="I20" t="n">
         <v>244.4256223720105</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.58</v>
+        <v>-2.94</v>
       </c>
       <c r="L20" t="n">
         <v>7.27</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43846</v>
+        <v>43847</v>
       </c>
       <c r="H21" t="n">
-        <v>246.35</v>
+        <v>254.2</v>
       </c>
       <c r="I21" t="n">
         <v>253.1815614308625</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9</v>
+        <v>-4.12</v>
       </c>
       <c r="L21" t="n">
         <v>9.359999999999999</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.06</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43899</v>
+        <v>43901</v>
       </c>
       <c r="H22" t="n">
-        <v>264.4</v>
+        <v>253.95</v>
       </c>
       <c r="I22" t="n">
         <v>258.2963657357447</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K22" t="n">
-        <v>4.01</v>
+        <v>-0.1</v>
       </c>
       <c r="L22" t="n">
         <v>2.83</v>
@@ -1695,7 +1958,7 @@
         <v>4.9</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>3.95</v>
       </c>
       <c r="O22" t="n">
         <v>3.19</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>17.21</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H23" t="n">
-        <v>230.45</v>
+        <v>240.95</v>
       </c>
       <c r="I23" t="n">
         <v>235.5604557239932</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K23" t="n">
-        <v>9.25</v>
+        <v>5.12</v>
       </c>
       <c r="L23" t="n">
         <v>3.9</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>15.84</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44278</v>
+        <v>44279</v>
       </c>
       <c r="H24" t="n">
-        <v>383.1</v>
+        <v>370.95</v>
       </c>
       <c r="I24" t="n">
         <v>374.8448841173281</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K24" t="n">
-        <v>59</v>
+        <v>53.95</v>
       </c>
       <c r="L24" t="n">
         <v>9.859999999999999</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>206</v>
+        <v>207</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>10</v>
+      </c>
+      <c r="U24" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>14.86</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44349</v>
+        <v>44350</v>
       </c>
       <c r="H25" t="n">
-        <v>400.9</v>
+        <v>410</v>
       </c>
       <c r="I25" t="n">
         <v>406.2847383515095</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.07</v>
+        <v>-10.53</v>
       </c>
       <c r="L25" t="n">
-        <v>10.1</v>
+        <v>12</v>
       </c>
       <c r="M25" t="n">
         <v>1.94</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H26" t="n">
-        <v>468.1</v>
+        <v>450.7</v>
       </c>
       <c r="I26" t="n">
         <v>451.0458316200894</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K26" t="n">
-        <v>14.17</v>
+        <v>9.93</v>
       </c>
       <c r="L26" t="n">
         <v>2.89</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>14.65</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44616</v>
+        <v>44617</v>
       </c>
       <c r="H27" t="n">
-        <v>405.5</v>
+        <v>417.35</v>
       </c>
       <c r="I27" t="n">
         <v>408.3143870805068</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K27" t="n">
-        <v>10.03</v>
+        <v>7.4</v>
       </c>
       <c r="L27" t="n">
         <v>9.43</v>
       </c>
       <c r="M27" t="n">
-        <v>1.71</v>
+        <v>2.59</v>
       </c>
       <c r="N27" t="n">
         <v>7.32</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>13.21</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H28" t="n">
-        <v>367.15</v>
+        <v>365</v>
       </c>
       <c r="I28" t="n">
         <v>367.0697016084097</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K28" t="n">
-        <v>-12.03</v>
+        <v>-12.54</v>
       </c>
       <c r="L28" t="n">
-        <v>13</v>
+        <v>14.82</v>
       </c>
       <c r="M28" t="n">
         <v>1.27</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>7.3</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H29" t="n">
-        <v>351.6</v>
+        <v>361.45</v>
       </c>
       <c r="I29" t="n">
         <v>360.917556218817</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K29" t="n">
-        <v>3.67</v>
+        <v>0.97</v>
       </c>
       <c r="L29" t="n">
-        <v>0.55</v>
+        <v>0.82</v>
       </c>
       <c r="M29" t="n">
         <v>1.04</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>11.49</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44722</v>
+        <v>44725</v>
       </c>
       <c r="H30" t="n">
-        <v>340.7</v>
+        <v>327.5</v>
       </c>
       <c r="I30" t="n">
         <v>329.4381974555157</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.74</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>6.05</v>
+        <v>10.25</v>
       </c>
       <c r="M30" t="n">
-        <v>0.89</v>
+        <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>2.29</v>
+        <v>3.87</v>
       </c>
       <c r="O30" t="n">
         <v>2.8</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>12.14</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44746</v>
+        <v>44747</v>
       </c>
       <c r="H31" t="n">
-        <v>349.75</v>
+        <v>356.45</v>
       </c>
       <c r="I31" t="n">
         <v>352.045472467895</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.79</v>
+        <v>-8.84</v>
       </c>
       <c r="L31" t="n">
-        <v>8.699999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M31" t="n">
         <v>1.43</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.05</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44844</v>
+        <v>44845</v>
       </c>
       <c r="H32" t="n">
-        <v>390.75</v>
+        <v>380.85</v>
       </c>
       <c r="I32" t="n">
         <v>383.1701523837187</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K32" t="n">
-        <v>9.619999999999999</v>
+        <v>6.85</v>
       </c>
       <c r="L32" t="n">
         <v>3.49</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.08</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45069</v>
+        <v>45070</v>
       </c>
       <c r="H33" t="n">
-        <v>266.1</v>
+        <v>276.2</v>
       </c>
       <c r="I33" t="n">
         <v>269.7488297915452</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K33" t="n">
-        <v>30.13</v>
+        <v>27.48</v>
       </c>
       <c r="L33" t="n">
         <v>3.7</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>152</v>
+        <v>153</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>8</v>
+      </c>
+      <c r="U33" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45152</v>
+        <v>45154</v>
       </c>
       <c r="H34" t="n">
-        <v>300.35</v>
+        <v>282.7</v>
       </c>
       <c r="I34" t="n">
         <v>286.7280371176562</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K34" t="n">
-        <v>8.74</v>
+        <v>2.35</v>
       </c>
       <c r="L34" t="n">
         <v>3.69</v>
@@ -2379,7 +2786,7 @@
         <v>1.04</v>
       </c>
       <c r="N34" t="n">
-        <v>2.72</v>
+        <v>5.88</v>
       </c>
       <c r="O34" t="n">
         <v>3.8</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.95</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45175</v>
+        <v>45176</v>
       </c>
       <c r="H35" t="n">
-        <v>309.25</v>
+        <v>313.45</v>
       </c>
       <c r="I35" t="n">
         <v>312.7369023471057</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.390000000000001</v>
+        <v>-10.88</v>
       </c>
       <c r="L35" t="n">
         <v>11.9</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>7.13</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45190</v>
+        <v>45191</v>
       </c>
       <c r="H36" t="n">
-        <v>300.8</v>
+        <v>296.05</v>
       </c>
       <c r="I36" t="n">
         <v>297.872727992918</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.04</v>
+        <v>-5.55</v>
       </c>
       <c r="L36" t="n">
-        <v>4.53</v>
+        <v>5.84</v>
       </c>
       <c r="M36" t="n">
         <v>0.28</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.18</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="H37" t="n">
-        <v>296.5</v>
+        <v>301.7</v>
       </c>
       <c r="I37" t="n">
         <v>298.0638583593198</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.15</v>
+        <v>-1.91</v>
       </c>
       <c r="L37" t="n">
         <v>7.06</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.95</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H38" t="n">
-        <v>310.25</v>
+        <v>300.25</v>
       </c>
       <c r="I38" t="n">
         <v>302.8995383415804</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K38" t="n">
-        <v>2.83</v>
+        <v>-0.48</v>
       </c>
       <c r="L38" t="n">
         <v>4.82</v>
@@ -2607,7 +3062,7 @@
         <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>2.35</v>
+        <v>3.22</v>
       </c>
       <c r="O38" t="n">
         <v>1.75</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.72</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="H39" t="n">
-        <v>281.05</v>
+        <v>290.2</v>
       </c>
       <c r="I39" t="n">
         <v>287.5827200719713</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K39" t="n">
-        <v>6.39</v>
+        <v>3.35</v>
       </c>
       <c r="L39" t="n">
         <v>5.15</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.67</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="H40" t="n">
-        <v>441.55</v>
+        <v>419.25</v>
       </c>
       <c r="I40" t="n">
         <v>431.4939586361543</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K40" t="n">
-        <v>52.15</v>
+        <v>44.47</v>
       </c>
       <c r="L40" t="n">
         <v>2.76</v>
@@ -2721,7 +3200,7 @@
         <v>2.4</v>
       </c>
       <c r="N40" t="n">
-        <v>4.76</v>
+        <v>5.05</v>
       </c>
       <c r="O40" t="n">
         <v>3.26</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>12.8</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H41" t="n">
-        <v>409.7</v>
+        <v>416.85</v>
       </c>
       <c r="I41" t="n">
         <v>413.1064741002747</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K41" t="n">
-        <v>2.28</v>
+        <v>0.57</v>
       </c>
       <c r="L41" t="n">
         <v>6.54</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="H42" t="n">
-        <v>395.8</v>
+        <v>375.3</v>
       </c>
       <c r="I42" t="n">
         <v>386.7737897393045</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.05</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>7.9</v>
+        <v>10.28</v>
       </c>
       <c r="M42" t="n">
         <v>2.07</v>
       </c>
       <c r="N42" t="n">
-        <v>2.23</v>
+        <v>5.18</v>
       </c>
       <c r="O42" t="n">
         <v>1.75</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.83</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H43" t="n">
-        <v>343.4</v>
+        <v>370</v>
       </c>
       <c r="I43" t="n">
         <v>367.3441096927709</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K43" t="n">
-        <v>8.5</v>
+        <v>1.41</v>
       </c>
       <c r="L43" t="n">
         <v>5.48</v>
@@ -2892,7 +3407,7 @@
         <v>1.46</v>
       </c>
       <c r="N43" t="n">
-        <v>2.14</v>
+        <v>7.75</v>
       </c>
       <c r="O43" t="n">
         <v>-5.18</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>13.86</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H44" t="n">
-        <v>342.25</v>
+        <v>330.9</v>
       </c>
       <c r="I44" t="n">
         <v>331.1828991507614</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K44" t="n">
-        <v>-7.5</v>
+        <v>-10.57</v>
       </c>
       <c r="L44" t="n">
-        <v>10.39</v>
+        <v>11.93</v>
       </c>
       <c r="M44" t="n">
         <v>1.27</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,25 +3524,25 @@
         <v>12.35</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45727</v>
+        <v>45728</v>
       </c>
       <c r="H45" t="n">
-        <v>346</v>
+        <v>357.65</v>
       </c>
       <c r="I45" t="n">
         <v>356.2626784815146</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.56</v>
+        <v>-8.08</v>
       </c>
       <c r="L45" t="n">
-        <v>5.94</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>0.74</v>
+        <v>1.05</v>
       </c>
       <c r="N45" t="n">
         <v>5.33</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>10.65</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H46" t="n">
-        <v>335.55</v>
+        <v>329.3</v>
       </c>
       <c r="I46" t="n">
         <v>330.2577742369501</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.18</v>
+        <v>-7.93</v>
       </c>
       <c r="L46" t="n">
-        <v>6.82</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M46" t="n">
         <v>0.65</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>9.77</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="H47" t="n">
-        <v>339.45</v>
+        <v>353.15</v>
       </c>
       <c r="I47" t="n">
         <v>352.9451824002192</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.08</v>
+        <v>-7.24</v>
       </c>
       <c r="L47" t="n">
-        <v>4.95</v>
+        <v>7.96</v>
       </c>
       <c r="M47" t="n">
         <v>4.63</v>
       </c>
       <c r="N47" t="n">
-        <v>2.18</v>
+        <v>4.04</v>
       </c>
       <c r="O47" t="n">
         <v>-1.86</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.84</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H48" t="n">
-        <v>343.8</v>
+        <v>335.65</v>
       </c>
       <c r="I48" t="n">
         <v>336.0178549968836</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.65</v>
+        <v>-4.96</v>
       </c>
       <c r="L48" t="n">
         <v>10.8</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.49</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H49" t="n">
-        <v>232.69</v>
+        <v>244.06</v>
       </c>
       <c r="I49" t="n">
         <v>241.0413309277224</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K49" t="n">
-        <v>30.67</v>
+        <v>27.29</v>
       </c>
       <c r="L49" t="n">
         <v>5.24</v>
@@ -3234,7 +3821,7 @@
         <v>4.24</v>
       </c>
       <c r="N49" t="n">
-        <v>3.9</v>
+        <v>4.89</v>
       </c>
       <c r="O49" t="n">
         <v>-2.37</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U49" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>12.63</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H50" t="n">
-        <v>248</v>
+        <v>241.3</v>
       </c>
       <c r="I50" t="n">
         <v>244.2932646492879</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K50" t="n">
-        <v>1.61</v>
+        <v>-1.13</v>
       </c>
       <c r="L50" t="n">
         <v>4.9</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>10.24</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="H51" t="n">
-        <v>247.95</v>
+        <v>260.97</v>
       </c>
       <c r="I51" t="n">
         <v>251.7827006333791</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.76</v>
+        <v>-8.15</v>
       </c>
       <c r="L51" t="n">
-        <v>5.47</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M51" t="n">
         <v>3.17</v>
       </c>
       <c r="N51" t="n">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="O51" t="n">
         <v>-2.7</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>13.1</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H52" t="n">
-        <v>269.3</v>
+        <v>266.6</v>
       </c>
       <c r="I52" t="n">
         <v>266.846858588558</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K52" t="n">
-        <v>3.19</v>
+        <v>2.16</v>
       </c>
       <c r="L52" t="n">
         <v>4.85</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>10.6</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="H53" t="n">
-        <v>266.1</v>
+        <v>270</v>
       </c>
       <c r="I53" t="n">
         <v>267.4950754512776</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K53" t="n">
-        <v>0.19</v>
+        <v>-1.28</v>
       </c>
       <c r="L53" t="n">
         <v>5.59</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>8.99</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="H54" t="n">
-        <v>247.55</v>
+        <v>245.4</v>
       </c>
       <c r="I54" t="n">
         <v>245.7227549096991</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>-8.31</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>8.869999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="M54" t="n">
         <v>-0</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3579,6 +4238,14 @@
       <c r="Q55" t="n">
         <v>54</v>
       </c>
+      <c r="R55" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7993,7 +8660,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.90000000000001</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="6">
@@ -8003,7 +8670,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -8013,7 +8680,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8">
@@ -8023,7 +8690,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -8033,7 +8700,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -8043,7 +8710,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>140.6</v>
       </c>
     </row>
     <row r="11">
@@ -8053,7 +8720,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -8063,7 +8730,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -8073,7 +8740,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.1</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="14">
@@ -8083,7 +8750,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.91</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15">
@@ -8093,7 +8760,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.04</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="16">
@@ -8103,7 +8770,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.69</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="17">
@@ -8113,7 +8780,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>59</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="18">
@@ -8123,7 +8790,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.2</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="19">
@@ -8133,7 +8800,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.49</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="20">
@@ -8143,7 +8810,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.94</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="21">
@@ -8153,7 +8820,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.58</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="22">
@@ -8163,7 +8830,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -8173,7 +8840,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -8183,7 +8850,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.16</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="25">
@@ -8193,7 +8860,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.39</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="26">
@@ -8203,7 +8870,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.21</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="27">
@@ -8223,7 +8890,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
